--- a/00_プロジェクト計画/【チーム演習】見積り決裁シート（責任者作成）.xlsx
+++ b/00_プロジェクト計画/【チーム演習】見積り決裁シート（責任者作成）.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\230451055\Downloads\【チーム演習】ドキュメント\ソフトウェアエンジニアリング入門配布資料\演習用ドキュメント\1．プロジェクト計画\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kyoceragp-my.sharepoint.com/personal/sachiko_enomoto_xm_kyocera_jp/Documents/ドキュメント/研修資料/チーム演習/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A8BD341-A121-4711-B9B4-558C657F54A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{B2B165AB-B803-4E29-BF27-037C0453B023}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C4BD9D4-5215-45D1-9A17-B554229F7060}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19290" yWindow="-4095" windowWidth="19380" windowHeight="10260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="見積り決裁シート" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="36">
   <si>
     <r>
       <rPr>
@@ -216,6 +216,13 @@
   <si>
     <t>2026年　6月　24日</t>
     <phoneticPr fontId="20"/>
+  </si>
+  <si>
+    <t>K2026-Z0011</t>
+    <phoneticPr fontId="20"/>
+  </si>
+  <si>
+    <t>確定</t>
   </si>
 </sst>
 </file>
@@ -1049,8 +1056,13 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1067,7 +1079,6 @@
     <xf numFmtId="38" fontId="7" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="38" fontId="7" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1096,6 +1107,44 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1112,7 +1161,6 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1125,30 +1173,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -1206,32 +1230,15 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1452,53 +1459,53 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:BL952"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="2" width="1.7109375" customWidth="1"/>
-    <col min="3" max="3" width="2.140625" customWidth="1"/>
-    <col min="4" max="4" width="2.85546875" customWidth="1"/>
-    <col min="5" max="5" width="5.7109375" customWidth="1"/>
-    <col min="6" max="9" width="3.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.42578125" customWidth="1"/>
-    <col min="11" max="12" width="3.7109375" customWidth="1"/>
-    <col min="13" max="30" width="4.140625" customWidth="1"/>
-    <col min="31" max="31" width="1.7109375" customWidth="1"/>
-    <col min="32" max="64" width="3.7109375" customWidth="1"/>
+    <col min="1" max="2" width="1.7265625" customWidth="1"/>
+    <col min="3" max="3" width="2.1796875" customWidth="1"/>
+    <col min="4" max="4" width="2.81640625" customWidth="1"/>
+    <col min="5" max="5" width="5.7265625" customWidth="1"/>
+    <col min="6" max="9" width="3.7265625" customWidth="1"/>
+    <col min="10" max="10" width="4.453125" customWidth="1"/>
+    <col min="11" max="12" width="3.7265625" customWidth="1"/>
+    <col min="13" max="30" width="4.1796875" customWidth="1"/>
+    <col min="31" max="31" width="1.7265625" customWidth="1"/>
+    <col min="32" max="64" width="3.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:64" ht="36" customHeight="1">
       <c r="A1" s="2"/>
-      <c r="B1" s="43" t="s">
+      <c r="B1" s="59" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
-      <c r="J1" s="44"/>
-      <c r="K1" s="44"/>
-      <c r="L1" s="44"/>
-      <c r="M1" s="44"/>
-      <c r="N1" s="44"/>
-      <c r="O1" s="44"/>
-      <c r="P1" s="44"/>
-      <c r="Q1" s="44"/>
-      <c r="R1" s="44"/>
-      <c r="S1" s="44"/>
-      <c r="T1" s="44"/>
-      <c r="U1" s="44"/>
-      <c r="V1" s="44"/>
-      <c r="W1" s="44"/>
-      <c r="X1" s="44"/>
-      <c r="Y1" s="44"/>
-      <c r="Z1" s="44"/>
-      <c r="AA1" s="44"/>
-      <c r="AB1" s="44"/>
-      <c r="AC1" s="44"/>
-      <c r="AD1" s="45"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="60"/>
+      <c r="F1" s="60"/>
+      <c r="G1" s="60"/>
+      <c r="H1" s="60"/>
+      <c r="I1" s="60"/>
+      <c r="J1" s="60"/>
+      <c r="K1" s="60"/>
+      <c r="L1" s="60"/>
+      <c r="M1" s="60"/>
+      <c r="N1" s="60"/>
+      <c r="O1" s="60"/>
+      <c r="P1" s="60"/>
+      <c r="Q1" s="60"/>
+      <c r="R1" s="60"/>
+      <c r="S1" s="60"/>
+      <c r="T1" s="60"/>
+      <c r="U1" s="60"/>
+      <c r="V1" s="60"/>
+      <c r="W1" s="60"/>
+      <c r="X1" s="60"/>
+      <c r="Y1" s="60"/>
+      <c r="Z1" s="60"/>
+      <c r="AA1" s="60"/>
+      <c r="AB1" s="60"/>
+      <c r="AC1" s="60"/>
+      <c r="AD1" s="61"/>
       <c r="AE1" s="3"/>
       <c r="AF1" s="4"/>
       <c r="AG1" s="4"/>
@@ -1562,13 +1569,13 @@
       <c r="Y2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="Z2" s="46" t="s">
+      <c r="Z2" s="62" t="s">
         <v>33</v>
       </c>
-      <c r="AA2" s="47"/>
-      <c r="AB2" s="47"/>
-      <c r="AC2" s="47"/>
-      <c r="AD2" s="48"/>
+      <c r="AA2" s="63"/>
+      <c r="AB2" s="63"/>
+      <c r="AC2" s="63"/>
+      <c r="AD2" s="64"/>
       <c r="AE2" s="5"/>
       <c r="AF2" s="4"/>
       <c r="AG2" s="4"/>
@@ -1606,41 +1613,41 @@
     </row>
     <row r="3" spans="1:64" ht="30" customHeight="1">
       <c r="A3" s="5"/>
-      <c r="B3" s="49" t="s">
+      <c r="B3" s="65" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="33"/>
-      <c r="F3" s="50" t="s">
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="66" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="28"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="52" t="s">
+      <c r="G3" s="17"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="67" t="s">
         <v>4</v>
       </c>
-      <c r="J3" s="28"/>
-      <c r="K3" s="28"/>
-      <c r="L3" s="28"/>
-      <c r="M3" s="28"/>
-      <c r="N3" s="28"/>
-      <c r="O3" s="28"/>
-      <c r="P3" s="28"/>
-      <c r="Q3" s="28"/>
-      <c r="R3" s="28"/>
-      <c r="S3" s="28"/>
-      <c r="T3" s="28"/>
-      <c r="U3" s="28"/>
-      <c r="V3" s="28"/>
-      <c r="W3" s="28"/>
-      <c r="X3" s="28"/>
-      <c r="Y3" s="28"/>
-      <c r="Z3" s="28"/>
-      <c r="AA3" s="28"/>
-      <c r="AB3" s="28"/>
-      <c r="AC3" s="28"/>
-      <c r="AD3" s="17"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="17"/>
+      <c r="L3" s="17"/>
+      <c r="M3" s="17"/>
+      <c r="N3" s="17"/>
+      <c r="O3" s="17"/>
+      <c r="P3" s="17"/>
+      <c r="Q3" s="17"/>
+      <c r="R3" s="17"/>
+      <c r="S3" s="17"/>
+      <c r="T3" s="17"/>
+      <c r="U3" s="17"/>
+      <c r="V3" s="17"/>
+      <c r="W3" s="17"/>
+      <c r="X3" s="17"/>
+      <c r="Y3" s="17"/>
+      <c r="Z3" s="17"/>
+      <c r="AA3" s="17"/>
+      <c r="AB3" s="17"/>
+      <c r="AC3" s="17"/>
+      <c r="AD3" s="20"/>
       <c r="AE3" s="5"/>
       <c r="AF3" s="4"/>
       <c r="AG3" s="4"/>
@@ -1678,39 +1685,39 @@
     </row>
     <row r="4" spans="1:64" ht="30" customHeight="1">
       <c r="A4" s="5"/>
-      <c r="B4" s="24"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="26"/>
-      <c r="F4" s="53" t="s">
+      <c r="B4" s="27"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="54"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="56" t="s">
+      <c r="G4" s="69"/>
+      <c r="H4" s="70"/>
+      <c r="I4" s="71" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="54"/>
-      <c r="K4" s="54"/>
-      <c r="L4" s="54"/>
-      <c r="M4" s="54"/>
-      <c r="N4" s="54"/>
-      <c r="O4" s="54"/>
-      <c r="P4" s="54"/>
-      <c r="Q4" s="54"/>
-      <c r="R4" s="54"/>
-      <c r="S4" s="54"/>
-      <c r="T4" s="54"/>
-      <c r="U4" s="54"/>
-      <c r="V4" s="54"/>
-      <c r="W4" s="54"/>
-      <c r="X4" s="54"/>
-      <c r="Y4" s="54"/>
-      <c r="Z4" s="54"/>
-      <c r="AA4" s="54"/>
-      <c r="AB4" s="54"/>
-      <c r="AC4" s="54"/>
-      <c r="AD4" s="57"/>
+      <c r="J4" s="69"/>
+      <c r="K4" s="69"/>
+      <c r="L4" s="69"/>
+      <c r="M4" s="69"/>
+      <c r="N4" s="69"/>
+      <c r="O4" s="69"/>
+      <c r="P4" s="69"/>
+      <c r="Q4" s="69"/>
+      <c r="R4" s="69"/>
+      <c r="S4" s="69"/>
+      <c r="T4" s="69"/>
+      <c r="U4" s="69"/>
+      <c r="V4" s="69"/>
+      <c r="W4" s="69"/>
+      <c r="X4" s="69"/>
+      <c r="Y4" s="69"/>
+      <c r="Z4" s="69"/>
+      <c r="AA4" s="69"/>
+      <c r="AB4" s="69"/>
+      <c r="AC4" s="69"/>
+      <c r="AD4" s="72"/>
       <c r="AE4" s="5"/>
       <c r="AF4" s="4"/>
       <c r="AG4" s="4"/>
@@ -1748,43 +1755,45 @@
     </row>
     <row r="5" spans="1:64" ht="30" customHeight="1">
       <c r="A5" s="9"/>
-      <c r="B5" s="63" t="s">
+      <c r="B5" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="28"/>
-      <c r="D5" s="28"/>
-      <c r="E5" s="51"/>
-      <c r="F5" s="64"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="28"/>
-      <c r="I5" s="28"/>
-      <c r="J5" s="17"/>
-      <c r="K5" s="65" t="s">
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5" s="17"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="17"/>
+      <c r="J5" s="20"/>
+      <c r="K5" s="98" t="s">
         <v>8</v>
       </c>
-      <c r="L5" s="28"/>
-      <c r="M5" s="28"/>
-      <c r="N5" s="28"/>
-      <c r="O5" s="51"/>
-      <c r="P5" s="66" t="s">
+      <c r="L5" s="17"/>
+      <c r="M5" s="17"/>
+      <c r="N5" s="17"/>
+      <c r="O5" s="18"/>
+      <c r="P5" s="99" t="s">
         <v>9</v>
       </c>
-      <c r="Q5" s="28"/>
-      <c r="R5" s="28"/>
-      <c r="S5" s="28"/>
-      <c r="T5" s="28"/>
-      <c r="U5" s="28"/>
-      <c r="V5" s="28"/>
-      <c r="W5" s="28"/>
-      <c r="X5" s="28"/>
-      <c r="Y5" s="28"/>
-      <c r="Z5" s="28"/>
-      <c r="AA5" s="28"/>
-      <c r="AB5" s="67"/>
-      <c r="AC5" s="16" t="s">
+      <c r="Q5" s="17"/>
+      <c r="R5" s="17"/>
+      <c r="S5" s="17"/>
+      <c r="T5" s="17"/>
+      <c r="U5" s="17"/>
+      <c r="V5" s="17"/>
+      <c r="W5" s="17"/>
+      <c r="X5" s="17"/>
+      <c r="Y5" s="17"/>
+      <c r="Z5" s="17"/>
+      <c r="AA5" s="17"/>
+      <c r="AB5" s="100"/>
+      <c r="AC5" s="101" t="s">
         <v>10</v>
       </c>
-      <c r="AD5" s="17"/>
+      <c r="AD5" s="20"/>
       <c r="AE5" s="5"/>
       <c r="AF5" s="4"/>
       <c r="AG5" s="4"/>
@@ -1822,43 +1831,43 @@
     </row>
     <row r="6" spans="1:64" ht="11.25" customHeight="1">
       <c r="A6" s="5"/>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="61" t="s">
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="49" t="s">
         <v>32</v>
       </c>
-      <c r="G6" s="93"/>
-      <c r="H6" s="93"/>
-      <c r="I6" s="93"/>
-      <c r="J6" s="94"/>
-      <c r="K6" s="58" t="s">
+      <c r="G6" s="50"/>
+      <c r="H6" s="50"/>
+      <c r="I6" s="50"/>
+      <c r="J6" s="51"/>
+      <c r="K6" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="L6" s="19"/>
-      <c r="M6" s="19"/>
-      <c r="N6" s="19"/>
-      <c r="O6" s="20"/>
-      <c r="P6" s="101" t="s">
+      <c r="L6" s="22"/>
+      <c r="M6" s="22"/>
+      <c r="N6" s="22"/>
+      <c r="O6" s="23"/>
+      <c r="P6" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="Q6" s="19"/>
-      <c r="R6" s="19"/>
-      <c r="S6" s="19"/>
-      <c r="T6" s="19"/>
-      <c r="U6" s="19"/>
-      <c r="V6" s="19"/>
-      <c r="W6" s="19"/>
-      <c r="X6" s="19"/>
-      <c r="Y6" s="19"/>
-      <c r="Z6" s="19"/>
-      <c r="AA6" s="19"/>
-      <c r="AB6" s="19"/>
-      <c r="AC6" s="19"/>
-      <c r="AD6" s="59"/>
+      <c r="Q6" s="22"/>
+      <c r="R6" s="22"/>
+      <c r="S6" s="22"/>
+      <c r="T6" s="22"/>
+      <c r="U6" s="22"/>
+      <c r="V6" s="22"/>
+      <c r="W6" s="22"/>
+      <c r="X6" s="22"/>
+      <c r="Y6" s="22"/>
+      <c r="Z6" s="22"/>
+      <c r="AA6" s="22"/>
+      <c r="AB6" s="22"/>
+      <c r="AC6" s="22"/>
+      <c r="AD6" s="47"/>
       <c r="AE6" s="5"/>
       <c r="AF6" s="4"/>
       <c r="AG6" s="4"/>
@@ -1896,35 +1905,35 @@
     </row>
     <row r="7" spans="1:64" ht="11.25" customHeight="1">
       <c r="A7" s="5"/>
-      <c r="B7" s="21"/>
-      <c r="C7" s="22"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="23"/>
-      <c r="F7" s="95"/>
-      <c r="G7" s="96"/>
-      <c r="H7" s="96"/>
-      <c r="I7" s="96"/>
-      <c r="J7" s="97"/>
-      <c r="K7" s="21"/>
-      <c r="L7" s="22"/>
-      <c r="M7" s="22"/>
-      <c r="N7" s="22"/>
-      <c r="O7" s="23"/>
-      <c r="P7" s="60"/>
-      <c r="Q7" s="22"/>
-      <c r="R7" s="22"/>
-      <c r="S7" s="22"/>
-      <c r="T7" s="22"/>
-      <c r="U7" s="22"/>
-      <c r="V7" s="22"/>
-      <c r="W7" s="22"/>
-      <c r="X7" s="22"/>
-      <c r="Y7" s="22"/>
-      <c r="Z7" s="22"/>
-      <c r="AA7" s="22"/>
-      <c r="AB7" s="22"/>
-      <c r="AC7" s="22"/>
-      <c r="AD7" s="41"/>
+      <c r="B7" s="24"/>
+      <c r="C7" s="25"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="26"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="53"/>
+      <c r="H7" s="53"/>
+      <c r="I7" s="53"/>
+      <c r="J7" s="54"/>
+      <c r="K7" s="24"/>
+      <c r="L7" s="25"/>
+      <c r="M7" s="25"/>
+      <c r="N7" s="25"/>
+      <c r="O7" s="26"/>
+      <c r="P7" s="48"/>
+      <c r="Q7" s="25"/>
+      <c r="R7" s="25"/>
+      <c r="S7" s="25"/>
+      <c r="T7" s="25"/>
+      <c r="U7" s="25"/>
+      <c r="V7" s="25"/>
+      <c r="W7" s="25"/>
+      <c r="X7" s="25"/>
+      <c r="Y7" s="25"/>
+      <c r="Z7" s="25"/>
+      <c r="AA7" s="25"/>
+      <c r="AB7" s="25"/>
+      <c r="AC7" s="25"/>
+      <c r="AD7" s="43"/>
       <c r="AE7" s="5"/>
       <c r="AF7" s="4"/>
       <c r="AG7" s="4"/>
@@ -1962,35 +1971,35 @@
     </row>
     <row r="8" spans="1:64" ht="11.25" customHeight="1">
       <c r="A8" s="5"/>
-      <c r="B8" s="24"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="26"/>
-      <c r="F8" s="98"/>
-      <c r="G8" s="99"/>
-      <c r="H8" s="99"/>
-      <c r="I8" s="99"/>
-      <c r="J8" s="100"/>
-      <c r="K8" s="24"/>
-      <c r="L8" s="25"/>
-      <c r="M8" s="25"/>
-      <c r="N8" s="25"/>
-      <c r="O8" s="26"/>
-      <c r="P8" s="38"/>
-      <c r="Q8" s="25"/>
-      <c r="R8" s="25"/>
-      <c r="S8" s="25"/>
-      <c r="T8" s="25"/>
-      <c r="U8" s="25"/>
-      <c r="V8" s="25"/>
-      <c r="W8" s="25"/>
-      <c r="X8" s="25"/>
-      <c r="Y8" s="25"/>
-      <c r="Z8" s="25"/>
-      <c r="AA8" s="25"/>
-      <c r="AB8" s="25"/>
-      <c r="AC8" s="25"/>
-      <c r="AD8" s="42"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="55"/>
+      <c r="G8" s="56"/>
+      <c r="H8" s="56"/>
+      <c r="I8" s="56"/>
+      <c r="J8" s="57"/>
+      <c r="K8" s="27"/>
+      <c r="L8" s="28"/>
+      <c r="M8" s="28"/>
+      <c r="N8" s="28"/>
+      <c r="O8" s="29"/>
+      <c r="P8" s="40"/>
+      <c r="Q8" s="28"/>
+      <c r="R8" s="28"/>
+      <c r="S8" s="28"/>
+      <c r="T8" s="28"/>
+      <c r="U8" s="28"/>
+      <c r="V8" s="28"/>
+      <c r="W8" s="28"/>
+      <c r="X8" s="28"/>
+      <c r="Y8" s="28"/>
+      <c r="Z8" s="28"/>
+      <c r="AA8" s="28"/>
+      <c r="AB8" s="28"/>
+      <c r="AC8" s="28"/>
+      <c r="AD8" s="44"/>
       <c r="AE8" s="5"/>
       <c r="AF8" s="4"/>
       <c r="AG8" s="4"/>
@@ -2028,40 +2037,40 @@
     </row>
     <row r="9" spans="1:64" ht="15" customHeight="1">
       <c r="A9" s="5"/>
-      <c r="B9" s="31" t="s">
+      <c r="B9" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="32"/>
-      <c r="D9" s="32"/>
-      <c r="E9" s="32"/>
-      <c r="F9" s="33"/>
-      <c r="G9" s="62" t="s">
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="35"/>
+      <c r="G9" s="58" t="s">
         <v>14</v>
       </c>
-      <c r="H9" s="28"/>
-      <c r="I9" s="28"/>
-      <c r="J9" s="51"/>
-      <c r="K9" s="27">
+      <c r="H9" s="17"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="18"/>
+      <c r="K9" s="30">
         <v>2772000</v>
       </c>
-      <c r="L9" s="28"/>
-      <c r="M9" s="28"/>
-      <c r="N9" s="28"/>
-      <c r="O9" s="28"/>
-      <c r="P9" s="28"/>
-      <c r="Q9" s="28"/>
-      <c r="R9" s="28"/>
-      <c r="S9" s="28"/>
-      <c r="T9" s="28"/>
-      <c r="U9" s="28"/>
-      <c r="V9" s="28"/>
-      <c r="W9" s="28"/>
-      <c r="X9" s="28"/>
-      <c r="Y9" s="28"/>
-      <c r="Z9" s="28"/>
-      <c r="AA9" s="28"/>
-      <c r="AB9" s="28"/>
-      <c r="AC9" s="28"/>
+      <c r="L9" s="17"/>
+      <c r="M9" s="17"/>
+      <c r="N9" s="17"/>
+      <c r="O9" s="17"/>
+      <c r="P9" s="17"/>
+      <c r="Q9" s="17"/>
+      <c r="R9" s="17"/>
+      <c r="S9" s="17"/>
+      <c r="T9" s="17"/>
+      <c r="U9" s="17"/>
+      <c r="V9" s="17"/>
+      <c r="W9" s="17"/>
+      <c r="X9" s="17"/>
+      <c r="Y9" s="17"/>
+      <c r="Z9" s="17"/>
+      <c r="AA9" s="17"/>
+      <c r="AB9" s="17"/>
+      <c r="AC9" s="17"/>
       <c r="AD9" s="10" t="s">
         <v>15</v>
       </c>
@@ -2102,23 +2111,23 @@
     </row>
     <row r="10" spans="1:64" ht="15" customHeight="1">
       <c r="A10" s="5"/>
-      <c r="B10" s="21"/>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="23"/>
-      <c r="G10" s="34" t="s">
+      <c r="B10" s="24"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="H10" s="30"/>
-      <c r="I10" s="30"/>
-      <c r="J10" s="35"/>
-      <c r="K10" s="36">
+      <c r="H10" s="32"/>
+      <c r="I10" s="32"/>
+      <c r="J10" s="37"/>
+      <c r="K10" s="38">
         <v>0</v>
       </c>
-      <c r="L10" s="30"/>
-      <c r="M10" s="30"/>
-      <c r="N10" s="30"/>
+      <c r="L10" s="32"/>
+      <c r="M10" s="32"/>
+      <c r="N10" s="32"/>
       <c r="O10" s="11" t="s">
         <v>17</v>
       </c>
@@ -2128,21 +2137,21 @@
       <c r="Q10" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="R10" s="29">
+      <c r="R10" s="31">
         <f>P10*K10</f>
         <v>0</v>
       </c>
-      <c r="S10" s="30"/>
-      <c r="T10" s="30"/>
-      <c r="U10" s="30"/>
-      <c r="V10" s="30"/>
-      <c r="W10" s="30"/>
-      <c r="X10" s="30"/>
-      <c r="Y10" s="30"/>
-      <c r="Z10" s="30"/>
-      <c r="AA10" s="30"/>
-      <c r="AB10" s="30"/>
-      <c r="AC10" s="30"/>
+      <c r="S10" s="32"/>
+      <c r="T10" s="32"/>
+      <c r="U10" s="32"/>
+      <c r="V10" s="32"/>
+      <c r="W10" s="32"/>
+      <c r="X10" s="32"/>
+      <c r="Y10" s="32"/>
+      <c r="Z10" s="32"/>
+      <c r="AA10" s="32"/>
+      <c r="AB10" s="32"/>
+      <c r="AC10" s="32"/>
       <c r="AD10" s="14" t="s">
         <v>15</v>
       </c>
@@ -2183,42 +2192,42 @@
     </row>
     <row r="11" spans="1:64" ht="15" customHeight="1">
       <c r="A11" s="5"/>
-      <c r="B11" s="21"/>
-      <c r="C11" s="22"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="23"/>
-      <c r="G11" s="37" t="s">
+      <c r="B11" s="24"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="26"/>
+      <c r="G11" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="H11" s="19"/>
-      <c r="I11" s="19"/>
-      <c r="J11" s="20"/>
-      <c r="K11" s="39">
+      <c r="H11" s="22"/>
+      <c r="I11" s="22"/>
+      <c r="J11" s="23"/>
+      <c r="K11" s="41">
         <f>K9+R10</f>
         <v>2772000</v>
       </c>
-      <c r="L11" s="19"/>
-      <c r="M11" s="19"/>
-      <c r="N11" s="19"/>
-      <c r="O11" s="19"/>
-      <c r="P11" s="19"/>
-      <c r="Q11" s="19"/>
-      <c r="R11" s="19"/>
-      <c r="S11" s="19"/>
-      <c r="T11" s="19"/>
-      <c r="U11" s="19"/>
-      <c r="V11" s="19"/>
-      <c r="W11" s="19"/>
-      <c r="X11" s="19"/>
-      <c r="Y11" s="19"/>
-      <c r="Z11" s="19"/>
-      <c r="AA11" s="19"/>
-      <c r="AB11" s="19"/>
-      <c r="AC11" s="40" t="s">
+      <c r="L11" s="22"/>
+      <c r="M11" s="22"/>
+      <c r="N11" s="22"/>
+      <c r="O11" s="22"/>
+      <c r="P11" s="22"/>
+      <c r="Q11" s="22"/>
+      <c r="R11" s="22"/>
+      <c r="S11" s="22"/>
+      <c r="T11" s="22"/>
+      <c r="U11" s="22"/>
+      <c r="V11" s="22"/>
+      <c r="W11" s="22"/>
+      <c r="X11" s="22"/>
+      <c r="Y11" s="22"/>
+      <c r="Z11" s="22"/>
+      <c r="AA11" s="22"/>
+      <c r="AB11" s="22"/>
+      <c r="AC11" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="AD11" s="41"/>
+      <c r="AD11" s="43"/>
       <c r="AE11" s="4"/>
       <c r="AF11" s="4"/>
       <c r="AG11" s="4"/>
@@ -2256,35 +2265,35 @@
     </row>
     <row r="12" spans="1:64" ht="15" customHeight="1">
       <c r="A12" s="5"/>
-      <c r="B12" s="24"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="25"/>
-      <c r="F12" s="26"/>
-      <c r="G12" s="38"/>
-      <c r="H12" s="25"/>
-      <c r="I12" s="25"/>
-      <c r="J12" s="26"/>
-      <c r="K12" s="38"/>
-      <c r="L12" s="25"/>
-      <c r="M12" s="25"/>
-      <c r="N12" s="25"/>
-      <c r="O12" s="25"/>
-      <c r="P12" s="25"/>
-      <c r="Q12" s="25"/>
-      <c r="R12" s="25"/>
-      <c r="S12" s="25"/>
-      <c r="T12" s="25"/>
-      <c r="U12" s="25"/>
-      <c r="V12" s="25"/>
-      <c r="W12" s="25"/>
-      <c r="X12" s="25"/>
-      <c r="Y12" s="25"/>
-      <c r="Z12" s="25"/>
-      <c r="AA12" s="25"/>
-      <c r="AB12" s="25"/>
-      <c r="AC12" s="25"/>
-      <c r="AD12" s="42"/>
+      <c r="B12" s="27"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="29"/>
+      <c r="G12" s="40"/>
+      <c r="H12" s="28"/>
+      <c r="I12" s="28"/>
+      <c r="J12" s="29"/>
+      <c r="K12" s="40"/>
+      <c r="L12" s="28"/>
+      <c r="M12" s="28"/>
+      <c r="N12" s="28"/>
+      <c r="O12" s="28"/>
+      <c r="P12" s="28"/>
+      <c r="Q12" s="28"/>
+      <c r="R12" s="28"/>
+      <c r="S12" s="28"/>
+      <c r="T12" s="28"/>
+      <c r="U12" s="28"/>
+      <c r="V12" s="28"/>
+      <c r="W12" s="28"/>
+      <c r="X12" s="28"/>
+      <c r="Y12" s="28"/>
+      <c r="Z12" s="28"/>
+      <c r="AA12" s="28"/>
+      <c r="AB12" s="28"/>
+      <c r="AC12" s="28"/>
+      <c r="AD12" s="44"/>
       <c r="AE12" s="4"/>
       <c r="AF12" s="4"/>
       <c r="AG12" s="4"/>
@@ -2322,43 +2331,45 @@
     </row>
     <row r="13" spans="1:64" ht="44.25" customHeight="1">
       <c r="A13" s="5"/>
-      <c r="B13" s="83" t="s">
+      <c r="B13" s="88" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="25"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="26"/>
-      <c r="F13" s="73" t="s">
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="G13" s="25"/>
-      <c r="H13" s="25"/>
-      <c r="I13" s="25"/>
-      <c r="J13" s="42"/>
-      <c r="K13" s="74" t="s">
+      <c r="G13" s="28"/>
+      <c r="H13" s="28"/>
+      <c r="I13" s="28"/>
+      <c r="J13" s="44"/>
+      <c r="K13" s="79" t="s">
         <v>22</v>
       </c>
-      <c r="L13" s="47"/>
-      <c r="M13" s="47"/>
-      <c r="N13" s="47"/>
-      <c r="O13" s="75"/>
-      <c r="P13" s="84">
+      <c r="L13" s="63"/>
+      <c r="M13" s="63"/>
+      <c r="N13" s="63"/>
+      <c r="O13" s="80"/>
+      <c r="P13" s="89">
         <v>46235</v>
       </c>
-      <c r="Q13" s="77"/>
-      <c r="R13" s="77"/>
-      <c r="S13" s="77"/>
-      <c r="T13" s="77"/>
-      <c r="U13" s="77"/>
-      <c r="V13" s="77"/>
-      <c r="W13" s="77"/>
-      <c r="X13" s="77"/>
-      <c r="Y13" s="77"/>
-      <c r="Z13" s="77"/>
-      <c r="AA13" s="85"/>
-      <c r="AB13" s="86"/>
-      <c r="AC13" s="47"/>
-      <c r="AD13" s="87"/>
+      <c r="Q13" s="82"/>
+      <c r="R13" s="82"/>
+      <c r="S13" s="82"/>
+      <c r="T13" s="82"/>
+      <c r="U13" s="82"/>
+      <c r="V13" s="82"/>
+      <c r="W13" s="82"/>
+      <c r="X13" s="82"/>
+      <c r="Y13" s="82"/>
+      <c r="Z13" s="82"/>
+      <c r="AA13" s="90"/>
+      <c r="AB13" s="91" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC13" s="63"/>
+      <c r="AD13" s="92"/>
       <c r="AE13" s="5"/>
       <c r="AF13" s="4"/>
       <c r="AG13" s="4"/>
@@ -2396,42 +2407,42 @@
     </row>
     <row r="14" spans="1:64" ht="22.5" customHeight="1">
       <c r="A14" s="5"/>
-      <c r="B14" s="76" t="s">
+      <c r="B14" s="81" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="77"/>
-      <c r="D14" s="77"/>
-      <c r="E14" s="77"/>
-      <c r="F14" s="77"/>
-      <c r="G14" s="77"/>
-      <c r="H14" s="77"/>
-      <c r="I14" s="77"/>
-      <c r="J14" s="78"/>
-      <c r="K14" s="79" t="s">
+      <c r="C14" s="82"/>
+      <c r="D14" s="82"/>
+      <c r="E14" s="82"/>
+      <c r="F14" s="82"/>
+      <c r="G14" s="82"/>
+      <c r="H14" s="82"/>
+      <c r="I14" s="82"/>
+      <c r="J14" s="83"/>
+      <c r="K14" s="84" t="s">
         <v>24</v>
       </c>
-      <c r="L14" s="32"/>
-      <c r="M14" s="32"/>
-      <c r="N14" s="32"/>
-      <c r="O14" s="33"/>
-      <c r="P14" s="88" t="e">
+      <c r="L14" s="34"/>
+      <c r="M14" s="34"/>
+      <c r="N14" s="34"/>
+      <c r="O14" s="35"/>
+      <c r="P14" s="93" t="e">
         <f>IF(K14=AZ17,"※3を参照",IF(K14=#REF!,"-",""))</f>
         <v>#REF!</v>
       </c>
-      <c r="Q14" s="77"/>
-      <c r="R14" s="77"/>
-      <c r="S14" s="77"/>
-      <c r="T14" s="77"/>
-      <c r="U14" s="77"/>
-      <c r="V14" s="77"/>
-      <c r="W14" s="77"/>
-      <c r="X14" s="77"/>
-      <c r="Y14" s="77"/>
-      <c r="Z14" s="77"/>
-      <c r="AA14" s="77"/>
-      <c r="AB14" s="77"/>
-      <c r="AC14" s="77"/>
-      <c r="AD14" s="78"/>
+      <c r="Q14" s="82"/>
+      <c r="R14" s="82"/>
+      <c r="S14" s="82"/>
+      <c r="T14" s="82"/>
+      <c r="U14" s="82"/>
+      <c r="V14" s="82"/>
+      <c r="W14" s="82"/>
+      <c r="X14" s="82"/>
+      <c r="Y14" s="82"/>
+      <c r="Z14" s="82"/>
+      <c r="AA14" s="82"/>
+      <c r="AB14" s="82"/>
+      <c r="AC14" s="82"/>
+      <c r="AD14" s="83"/>
       <c r="AE14" s="5"/>
       <c r="AL14" s="1"/>
       <c r="AM14" s="4"/>
@@ -2449,82 +2460,82 @@
     </row>
     <row r="15" spans="1:64" ht="22.5" customHeight="1">
       <c r="A15" s="5"/>
-      <c r="B15" s="80" t="s">
+      <c r="B15" s="85" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="32"/>
-      <c r="D15" s="32"/>
-      <c r="E15" s="32"/>
-      <c r="F15" s="32"/>
-      <c r="G15" s="32"/>
-      <c r="H15" s="32"/>
-      <c r="I15" s="32"/>
-      <c r="J15" s="81"/>
-      <c r="K15" s="79" t="s">
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="34"/>
+      <c r="G15" s="34"/>
+      <c r="H15" s="34"/>
+      <c r="I15" s="34"/>
+      <c r="J15" s="86"/>
+      <c r="K15" s="84" t="s">
         <v>26</v>
       </c>
-      <c r="L15" s="32"/>
-      <c r="M15" s="32"/>
-      <c r="N15" s="32"/>
-      <c r="O15" s="33"/>
-      <c r="P15" s="89" t="str">
+      <c r="L15" s="34"/>
+      <c r="M15" s="34"/>
+      <c r="N15" s="34"/>
+      <c r="O15" s="35"/>
+      <c r="P15" s="94" t="str">
         <f>IF(K15=AS17,"工事対象の作業は、エンジニアリング事業本部へ依頼して下さい。","")</f>
         <v/>
       </c>
-      <c r="Q15" s="90"/>
-      <c r="R15" s="90"/>
-      <c r="S15" s="90"/>
-      <c r="T15" s="90"/>
-      <c r="U15" s="90"/>
-      <c r="V15" s="90"/>
-      <c r="W15" s="90"/>
-      <c r="X15" s="90"/>
-      <c r="Y15" s="90"/>
-      <c r="Z15" s="90"/>
-      <c r="AA15" s="90"/>
-      <c r="AB15" s="90"/>
-      <c r="AC15" s="90"/>
-      <c r="AD15" s="91"/>
+      <c r="Q15" s="95"/>
+      <c r="R15" s="95"/>
+      <c r="S15" s="95"/>
+      <c r="T15" s="95"/>
+      <c r="U15" s="95"/>
+      <c r="V15" s="95"/>
+      <c r="W15" s="95"/>
+      <c r="X15" s="95"/>
+      <c r="Y15" s="95"/>
+      <c r="Z15" s="95"/>
+      <c r="AA15" s="95"/>
+      <c r="AB15" s="95"/>
+      <c r="AC15" s="95"/>
+      <c r="AD15" s="96"/>
       <c r="AE15" s="5"/>
       <c r="AL15" s="1"/>
     </row>
     <row r="16" spans="1:64" ht="18.75" customHeight="1">
       <c r="A16" s="5"/>
-      <c r="B16" s="68" t="s">
+      <c r="B16" s="73" t="s">
         <v>27</v>
       </c>
-      <c r="C16" s="30"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="30"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="30"/>
-      <c r="H16" s="30"/>
-      <c r="I16" s="30"/>
-      <c r="J16" s="69"/>
-      <c r="K16" s="82" t="s">
+      <c r="C16" s="32"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="32"/>
+      <c r="F16" s="32"/>
+      <c r="G16" s="32"/>
+      <c r="H16" s="32"/>
+      <c r="I16" s="32"/>
+      <c r="J16" s="74"/>
+      <c r="K16" s="87" t="s">
         <v>28</v>
       </c>
-      <c r="L16" s="30"/>
-      <c r="M16" s="30"/>
-      <c r="N16" s="30"/>
-      <c r="O16" s="35"/>
-      <c r="P16" s="92" t="s">
+      <c r="L16" s="32"/>
+      <c r="M16" s="32"/>
+      <c r="N16" s="32"/>
+      <c r="O16" s="37"/>
+      <c r="P16" s="97" t="s">
         <v>29</v>
       </c>
-      <c r="Q16" s="30"/>
-      <c r="R16" s="30"/>
-      <c r="S16" s="30"/>
-      <c r="T16" s="30"/>
-      <c r="U16" s="30"/>
-      <c r="V16" s="30"/>
-      <c r="W16" s="30"/>
-      <c r="X16" s="30"/>
-      <c r="Y16" s="30"/>
-      <c r="Z16" s="30"/>
-      <c r="AA16" s="30"/>
-      <c r="AB16" s="30"/>
-      <c r="AC16" s="30"/>
-      <c r="AD16" s="69"/>
+      <c r="Q16" s="32"/>
+      <c r="R16" s="32"/>
+      <c r="S16" s="32"/>
+      <c r="T16" s="32"/>
+      <c r="U16" s="32"/>
+      <c r="V16" s="32"/>
+      <c r="W16" s="32"/>
+      <c r="X16" s="32"/>
+      <c r="Y16" s="32"/>
+      <c r="Z16" s="32"/>
+      <c r="AA16" s="32"/>
+      <c r="AB16" s="32"/>
+      <c r="AC16" s="32"/>
+      <c r="AD16" s="74"/>
       <c r="AE16" s="5"/>
       <c r="AF16" s="4"/>
       <c r="AG16" s="4"/>
@@ -2549,41 +2560,41 @@
     </row>
     <row r="17" spans="1:64" ht="18.75" customHeight="1">
       <c r="A17" s="5"/>
-      <c r="B17" s="70" t="s">
+      <c r="B17" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="C17" s="54"/>
-      <c r="D17" s="54"/>
-      <c r="E17" s="54"/>
-      <c r="F17" s="54"/>
-      <c r="G17" s="54"/>
-      <c r="H17" s="54"/>
-      <c r="I17" s="54"/>
-      <c r="J17" s="57"/>
-      <c r="K17" s="71" t="s">
+      <c r="C17" s="69"/>
+      <c r="D17" s="69"/>
+      <c r="E17" s="69"/>
+      <c r="F17" s="69"/>
+      <c r="G17" s="69"/>
+      <c r="H17" s="69"/>
+      <c r="I17" s="69"/>
+      <c r="J17" s="72"/>
+      <c r="K17" s="76" t="s">
         <v>28</v>
       </c>
-      <c r="L17" s="54"/>
-      <c r="M17" s="54"/>
-      <c r="N17" s="54"/>
-      <c r="O17" s="55"/>
-      <c r="P17" s="72" t="s">
+      <c r="L17" s="69"/>
+      <c r="M17" s="69"/>
+      <c r="N17" s="69"/>
+      <c r="O17" s="70"/>
+      <c r="P17" s="77" t="s">
         <v>29</v>
       </c>
-      <c r="Q17" s="54"/>
-      <c r="R17" s="54"/>
-      <c r="S17" s="54"/>
-      <c r="T17" s="54"/>
-      <c r="U17" s="54"/>
-      <c r="V17" s="54"/>
-      <c r="W17" s="54"/>
-      <c r="X17" s="54"/>
-      <c r="Y17" s="54"/>
-      <c r="Z17" s="54"/>
-      <c r="AA17" s="54"/>
-      <c r="AB17" s="54"/>
-      <c r="AC17" s="54"/>
-      <c r="AD17" s="57"/>
+      <c r="Q17" s="69"/>
+      <c r="R17" s="69"/>
+      <c r="S17" s="69"/>
+      <c r="T17" s="69"/>
+      <c r="U17" s="69"/>
+      <c r="V17" s="69"/>
+      <c r="W17" s="69"/>
+      <c r="X17" s="69"/>
+      <c r="Y17" s="69"/>
+      <c r="Z17" s="69"/>
+      <c r="AA17" s="69"/>
+      <c r="AB17" s="69"/>
+      <c r="AC17" s="69"/>
+      <c r="AD17" s="72"/>
       <c r="AE17" s="5"/>
       <c r="AF17" s="4"/>
       <c r="AG17" s="4"/>
@@ -64318,11 +64329,10 @@
     </row>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="P14:AD14"/>
-    <mergeCell ref="P15:AD15"/>
     <mergeCell ref="P16:AD16"/>
     <mergeCell ref="K5:O5"/>
     <mergeCell ref="P5:AB5"/>
+    <mergeCell ref="AC5:AD5"/>
     <mergeCell ref="B16:J16"/>
     <mergeCell ref="B17:J17"/>
     <mergeCell ref="K17:O17"/>
@@ -64337,6 +64347,8 @@
     <mergeCell ref="B13:E13"/>
     <mergeCell ref="P13:AA13"/>
     <mergeCell ref="AB13:AD13"/>
+    <mergeCell ref="P14:AD14"/>
+    <mergeCell ref="P15:AD15"/>
     <mergeCell ref="B1:AD1"/>
     <mergeCell ref="Z2:AD2"/>
     <mergeCell ref="B3:E4"/>
@@ -64344,7 +64356,8 @@
     <mergeCell ref="I3:AD3"/>
     <mergeCell ref="F4:H4"/>
     <mergeCell ref="I4:AD4"/>
-    <mergeCell ref="AC5:AD5"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="F5:J5"/>
     <mergeCell ref="B6:E8"/>
     <mergeCell ref="K9:AC9"/>
     <mergeCell ref="R10:AC10"/>
@@ -64358,8 +64371,6 @@
     <mergeCell ref="P6:AD8"/>
     <mergeCell ref="F6:J8"/>
     <mergeCell ref="G9:J9"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="F5:J5"/>
   </mergeCells>
   <phoneticPr fontId="20"/>
   <dataValidations count="4">
